--- a/docs/حافز-المحطات.xlsx
+++ b/docs/حافز-المحطات.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المستهدف" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بطاقة الأداء" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المنهجية" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجعة الملف" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3444,7 +3445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3560,7 +3561,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>الظهور والسمعة</t>
+          <t>٩٠÷١٠٠=٠٫٩٠ — والملف كتبها ١٫٠٠</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3599,7 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>المحرّك الأول</t>
+          <t>٢٦٥÷٢٥٠ — صحيحة في الملف</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3647,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>التدقيق الخارجي</t>
+          <t>عدد الشكاوى المغلقة</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>٪</t>
+          <t>عدد</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -3660,13 +3661,13 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="H8" s="10">
         <f>IFERROR(G8/F8,0)</f>
@@ -3674,7 +3675,7 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>جهة مستقلة</t>
+          <t>كانت بلا وزن في الملف</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3685,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>التدقيق الداخلي — النظافة</t>
+          <t>التدقيق الخارجي</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3698,13 +3699,13 @@
         </is>
       </c>
       <c r="E9" s="28" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H9" s="10">
         <f>IFERROR(G9/F9,0)</f>
@@ -3712,7 +3713,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>داخلي</t>
+          <t>جهة مستقلة</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3723,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>التدقيق الداخلي — السلوك</t>
+          <t>التدقيق الداخلي — النظافة</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3739,10 +3740,10 @@
         <v>0.05</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H10" s="10">
         <f>IFERROR(G10/F10,0)</f>
@@ -3755,88 +3756,105 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr"/>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>التدقيق الداخلي — السلوك</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>٪</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>خدمة وتدقيق</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>90</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="H11" s="10">
+        <f>IFERROR(G11/F11,0)</f>
+        <v/>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>داخلي</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr"/>
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>الإجمالي المرجَّح</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr"/>
-      <c r="D11" s="24" t="inlineStr"/>
-      <c r="E11" s="32">
-        <f>SUM(E5:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="24" t="inlineStr"/>
-      <c r="G11" s="24" t="inlineStr"/>
-      <c r="H11" s="27">
-        <f>SUMPRODUCT(E5:E10,H5:H10)/SUM(E5:E10)</f>
-        <v/>
-      </c>
-      <c r="I11" s="24" t="inlineStr"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr"/>
+      <c r="D12" s="24" t="inlineStr"/>
+      <c r="E12" s="32">
+        <f>SUM(E5:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="24" t="inlineStr"/>
+      <c r="G12" s="24" t="inlineStr"/>
+      <c r="H12" s="27">
+        <f>SUMPRODUCT(E5:E11,H5:H11)/SUM(E5:E11)</f>
+        <v/>
+      </c>
+      <c r="I12" s="24" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>② الشروط النوعية — تُمنع بها الصرف ولا تُزاد بها</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>الشرط</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>مستوفى؟</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>ملاحظة المشرف</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>متابعة يومية للمبيعات</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I15" s="29" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>المتابعة الدورية على النظافة</t>
+          <t>متابعة يومية للمبيعات</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
@@ -3853,11 +3871,11 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>الحرص على تقديم أفضل خدمة</t>
+          <t>المتابعة الدورية على النظافة</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
@@ -3874,11 +3892,11 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>تقديم مناديل مجاناً للعملاء</t>
+          <t>الحرص على تقديم أفضل خدمة</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
@@ -3895,11 +3913,11 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>تنظيف الزجاج الأمامي للسيارات</t>
+          <t>تقديم مناديل مجاناً للعملاء</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
@@ -3916,11 +3934,11 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>تدريب العمال ومتابعتهم</t>
+          <t>تنظيف الزجاج الأمامي للسيارات</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
@@ -3935,8 +3953,29 @@
       </c>
       <c r="I20" s="29" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>تدريب العمال ومتابعتهم</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I21" s="29" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>الشروط النوعية بوابة لا وزن: عدم استيفاء أيٍّ منها يمنع الصرف، واستيفاؤها جميعاً لا يرفع المبلغ.</t>
         </is>
@@ -3946,10 +3985,10 @@
   <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A14:I14"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H10">
+  <conditionalFormatting sqref="H5:H11">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="3">
       <formula>1</formula>
     </cfRule>
@@ -3958,7 +3997,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H15 H16 H17 H18 H19 H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H16 H17 H18 H19 H20 H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"نعم,لا"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4340,4 +4379,544 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>مراجعة الملف الأصلي — رقماً رقماً</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ما يغيّر النتيجة أولاً، ثم ما يُفسد القياس، ثم ما هو سليم</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>① أخطاء حسابية — تغيّر النتيجة</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>الموضع</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>ما في الملف</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>الصحيح</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>الأثر</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>أيام لم تصل بياناتها</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>٢٠–٣٠ سبتمبر مُدخَلة صفراً لا مُتروكة فارغة</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>تُترك فارغة أو يُقسَم على أيامها</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>التحقيق يُقرأ ٥٩٪ بدل ٩٢٫٥٪ و٩٣٫١٪ — فيسقط ١٬٠٠٠ و٢٬٥٠٠ ريال عن ١٨ عاملاً ومديرَين</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>«2026 vs 2025»</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>الشرائع −١٫٨١ · العزيزية +٠٫٩٩</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>−٦٤٫٤٪ للشرائع</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>القسمة معكوسة: ٢٠٢٥÷٢٠٢٦ بدل العكس — الرقم بلا معنى كما هو</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>تقييم خرائط جوجل</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>٩٠ من ١٠٠ تُحتسب ١٫٠٠</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>٠٫٩٠</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>يرفع بطاقة الأداء بنقطة كاملة بلا استحقاق</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>عدد الشكاوى المغلقة</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>٢٧ من ٢٥ تُحتسب ١٫٠٠</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>١٫٠٨</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>السقف غير متسق: المبيعات ١٫٠٦ والجودة ١٫٥٠ بلا سقف</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>② عيوب بنيوية — لا تغيّر رقماً اليوم لكنها تُفسد القياس</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>الموضع</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>الحال</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ما يلزم</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>لماذا</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>مجموع الأوزان</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>٠٫٩٥ لا ١٫٠٠</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>توزيع الـ٥٪ الناقصة</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>النتيجة تُقسم على قاعدة ناقصة</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>مؤشرات بلا وزن</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>خمسة مؤشرات تُقاس ولا تدخل النتيجة</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>وزنٌ لكلٍّ أو حذفها</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>فئة المبيعات تأخذ «مبيعات الوقود» وحدها</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>الشريحة الوسطى</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>١٬٣٠٠ ريال عند «١٠٠٪» بالضبط</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>حدود صريحة: ٨٥–٩٩٫٩٩ · ١٠٠–١٠٤٫٩٩ · ١٠٥ فأكثر</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>لا تُدرَك عملياً إن كانت التالية «أكثر من ١٠٠٪»</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>نسبة المدير</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>٣٠٪ في الشرائع و١٥٪ في العزيزية</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>معيار واحد</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>لا سند للفارق في الملف</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>متوسط ٢٠٢٥ للعزيزية</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>١٠٬٠١٦ ريالاً</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>١٥٦٬٨٩٣ — أو تُحذف السنة</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>أشهر ٢٠٢٥ كلها أصفار إلا سبتمبر ١٬٢٥٥٬١٤٥ · والرقم لا يطابق أيّ حساب</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>نطاق الترويسة</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>مكتوب Jan-Aug والصف سبعة أشهر ٢٠٢٦</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>تطابق الترويسة مع البيانات</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>وأغسطس ٢٠٢٥ مفقود بينما سبتمبر ٢٠٢٥ موجود</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>وحدات القياس</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>JOD لتقييم جوجل · Ton للجودة</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>نقطة · نسبة</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>قالب منقول لم يُحوَّل، والصرف بالريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>③ وما هو سليم في الملف — يُقال إنصافاً</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>الموضع</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>الحال</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>الفحص</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>النتيجة</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>الميزانية اليومية الموحَّدة</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>٩٬٣٧٨ و٦١٬٨٠٦ ريالاً لكل يوم</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>تباين أيام الأسبوع</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>٠٫٨٩× إلى ١٫٠٧× فقط — فالتوحيد مبرَّر ولا يحتاج تشكيلاً</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>الإجمالي الإلكتروني</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>مجموع ٩١ و٩٥ والديزل</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>طوبقت المحطتان</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>مطابق إلى الهللة</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>الصفوف اليومية</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Act vs BU و٪ لكل يوم</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>أُعيد حسابها</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>صحيحة يوماً بيوم — الخلل في التجميع الشهري لا في اليوم</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>اشتقاق الميزانية</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>أغسطس × (١ + نسبة النمو)</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>طوبقت المحطتان</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>مطبَّقة بدقة: ٢٦٥٬٤٠٥×١٫٠٦ و١٬٧٣٢٬٨٨٤×١٫٠٧</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A20:F20"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>